--- a/output/details/2026-05-31/preprocessed_data.xlsx
+++ b/output/details/2026-05-31/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46173</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1180871047683038</v>
+        <v>-0.1249104862110448</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1326231289786719</v>
+        <v>-0.144878173471874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1324472631490006</v>
+        <v>-0.1445963787009085</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1157886378491995</v>
+        <v>-0.001754569706203391</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001695692953085159</v>
+        <v>0.001690424129690676</v>
       </c>
       <c r="G2" t="n">
-        <v>1.995112122021528</v>
+        <v>2.547266484576538</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4295570981383761</v>
+        <v>-0.2659981311925045</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
